--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129001049</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,1529 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130013075</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>577780</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6732102</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130013322</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92887</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>577899</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6732201</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130013408</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>577906</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6732164</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130013020</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92887</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>577778</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6732092</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130013129</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577838</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6732124</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130013164</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577835</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6732236</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridda över lite större yta.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130012857</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577715</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6731993</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 0.5 kv dm.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130013591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577858</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6732062</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130012879</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577729</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6731987</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130013582</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577854</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6732059</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130013410</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577906</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6732162</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130012862</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577735</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6731996</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130013015</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79087</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577777</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6732093</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130013075</v>
+        <v>130013322</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>92888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,39 +792,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577780</v>
+        <v>577899</v>
       </c>
       <c r="R3" t="n">
-        <v>6732102</v>
+        <v>6732201</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,42 +897,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013322</v>
+        <v>130013408</v>
       </c>
       <c r="B4" t="n">
-        <v>92887</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577899</v>
+        <v>577906</v>
       </c>
       <c r="R4" t="n">
-        <v>6732201</v>
+        <v>6732164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,50 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013408</v>
+        <v>130013075</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577906</v>
+        <v>577780</v>
       </c>
       <c r="R5" t="n">
-        <v>6732164</v>
+        <v>6732102</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1124,7 @@
         <v>130013020</v>
       </c>
       <c r="B6" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>130013129</v>
       </c>
       <c r="B7" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130013164</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>130012857</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130013591</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>130012879</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>130013582</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,59 +2071,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R14" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,45 +2178,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R15" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2267,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2272,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -2071,45 +2071,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R14" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,59 +2197,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R15" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2262,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,12 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -2071,59 +2071,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R14" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,45 +2178,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R15" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2267,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2272,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130013322</v>
       </c>
       <c r="B3" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>130013020</v>
       </c>
       <c r="B6" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>130013129</v>
       </c>
       <c r="B7" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130013164</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>130012857</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130013591</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>130012879</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>130013582</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,45 +2071,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R14" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,59 +2197,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R15" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2262,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,12 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130013075</v>
+        <v>130013322</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>92921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,39 +792,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577780</v>
+        <v>577899</v>
       </c>
       <c r="R3" t="n">
-        <v>6732102</v>
+        <v>6732201</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013408</v>
+        <v>130013075</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577906</v>
+        <v>577780</v>
       </c>
       <c r="R4" t="n">
-        <v>6732164</v>
+        <v>6732102</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,42 +1009,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013322</v>
+        <v>130013408</v>
       </c>
       <c r="B5" t="n">
-        <v>92921</v>
+        <v>57738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577899</v>
+        <v>577906</v>
       </c>
       <c r="R5" t="n">
-        <v>6732201</v>
+        <v>6732164</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130013322</v>
       </c>
       <c r="B3" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013075</v>
+        <v>130013408</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>57738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577780</v>
+        <v>577906</v>
       </c>
       <c r="R4" t="n">
-        <v>6732102</v>
+        <v>6732164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,50 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013408</v>
+        <v>130013075</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577906</v>
+        <v>577780</v>
       </c>
       <c r="R5" t="n">
-        <v>6732164</v>
+        <v>6732102</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1124,7 @@
         <v>130013020</v>
       </c>
       <c r="B6" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130013164</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>130012857</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130013591</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>130012879</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>130013582</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>130012862</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>130013322</v>
       </c>
       <c r="B3" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013408</v>
+        <v>130013075</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577906</v>
+        <v>577780</v>
       </c>
       <c r="R4" t="n">
-        <v>6732164</v>
+        <v>6732102</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,50 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013075</v>
+        <v>130013408</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577780</v>
+        <v>577906</v>
       </c>
       <c r="R5" t="n">
-        <v>6732102</v>
+        <v>6732164</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,7 +1124,7 @@
         <v>130013020</v>
       </c>
       <c r="B6" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>130013129</v>
       </c>
       <c r="B7" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>130013164</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>130012857</v>
       </c>
       <c r="B9" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>130013591</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>130012879</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>130013582</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,45 +2071,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R14" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,59 +2197,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R15" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2262,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,12 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -897,50 +897,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013075</v>
+        <v>130013408</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577780</v>
+        <v>577906</v>
       </c>
       <c r="R4" t="n">
-        <v>6732102</v>
+        <v>6732164</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,50 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013408</v>
+        <v>130013075</v>
       </c>
       <c r="B5" t="n">
-        <v>57823</v>
+        <v>5177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577906</v>
+        <v>577780</v>
       </c>
       <c r="R5" t="n">
-        <v>6732164</v>
+        <v>6732102</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -2071,59 +2071,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R14" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,45 +2178,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R15" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2267,7 +2262,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2272,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130013322</v>
+        <v>130013075</v>
       </c>
       <c r="B3" t="n">
-        <v>93010</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,43 +792,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577899</v>
+        <v>577780</v>
       </c>
       <c r="R3" t="n">
-        <v>6732201</v>
+        <v>6732102</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -860,7 +856,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +866,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,38 +893,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013408</v>
+        <v>130013322</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577906</v>
+        <v>577899</v>
       </c>
       <c r="R4" t="n">
-        <v>6732164</v>
+        <v>6732201</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,50 +1009,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013075</v>
+        <v>130013408</v>
       </c>
       <c r="B5" t="n">
-        <v>5177</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577780</v>
+        <v>577906</v>
       </c>
       <c r="R5" t="n">
-        <v>6732102</v>
+        <v>6732164</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -2071,45 +2071,59 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130013015</v>
+        <v>130012862</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577777</v>
+        <v>577735</v>
       </c>
       <c r="R14" t="n">
-        <v>6732093</v>
+        <v>6731996</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,59 +2197,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130012862</v>
+        <v>130013015</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577735</v>
+        <v>577777</v>
       </c>
       <c r="R15" t="n">
-        <v>6731996</v>
+        <v>6732093</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2262,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,12 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridda över ytan.</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129001049</v>
+        <v>130013237</v>
       </c>
       <c r="B2" t="n">
-        <v>92873</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kungsberg, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577788</v>
+        <v>577830</v>
       </c>
       <c r="R2" t="n">
-        <v>6732062</v>
+        <v>6732289</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130013408</v>
+        <v>130013020</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,39 +793,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577906</v>
+        <v>577778</v>
       </c>
       <c r="R3" t="n">
-        <v>6732164</v>
+        <v>6732092</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -856,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,50 +898,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130013075</v>
+        <v>130013322</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577780</v>
+        <v>577899</v>
       </c>
       <c r="R4" t="n">
-        <v>6732102</v>
+        <v>6732201</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,57 +1014,52 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130013322</v>
+        <v>129001049</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Kungsberg, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577899</v>
+        <v>577788</v>
       </c>
       <c r="R5" t="n">
-        <v>6732201</v>
+        <v>6732062</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,22 +1083,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:59</t>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,66 +1108,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130013020</v>
+        <v>130013015</v>
       </c>
       <c r="B6" t="n">
-        <v>93010</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577778</v>
+        <v>577777</v>
       </c>
       <c r="R6" t="n">
-        <v>6732092</v>
+        <v>6732093</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1240,7 +1230,7 @@
         <v>130013129</v>
       </c>
       <c r="B7" t="n">
-        <v>78937</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,59 +1334,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130013164</v>
+        <v>130013408</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577835</v>
+        <v>577906</v>
       </c>
       <c r="R8" t="n">
-        <v>6732236</v>
+        <v>6732164</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1438,12 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridda över lite större yta.</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,47 +1446,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130012857</v>
+        <v>130013075</v>
       </c>
       <c r="B9" t="n">
-        <v>98920</v>
+        <v>5179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1519,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577715</v>
+        <v>577780</v>
       </c>
       <c r="R9" t="n">
-        <v>6731993</v>
+        <v>6732102</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1554,7 +1521,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,12 +1531,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:55</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Bladrosetter över ca 0.5 kv dm.</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,47 +1558,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130013591</v>
+        <v>130013410</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>8455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1645,10 +1598,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577858</v>
+        <v>577906</v>
       </c>
       <c r="R10" t="n">
-        <v>6732062</v>
+        <v>6732162</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1643,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130012879</v>
+        <v>130012857</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,12 +1705,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1766,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577729</v>
+        <v>577715</v>
       </c>
       <c r="R11" t="n">
-        <v>6731987</v>
+        <v>6731993</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1801,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1764,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bladrosetter över ca 0.5 kv dm.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,10 +1796,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130013582</v>
+        <v>130012862</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,12 +1826,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1883,14 +1841,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577854</v>
+        <v>577735</v>
       </c>
       <c r="R12" t="n">
-        <v>6732059</v>
+        <v>6731996</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1922,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1890,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spridda över ytan.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,50 +1922,59 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130013410</v>
+        <v>130012879</v>
       </c>
       <c r="B13" t="n">
-        <v>8451</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577906</v>
+        <v>577729</v>
       </c>
       <c r="R13" t="n">
-        <v>6732162</v>
+        <v>6731987</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2034,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130012862</v>
+        <v>130013164</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2101,12 +2073,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2120,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577735</v>
+        <v>577835</v>
       </c>
       <c r="R14" t="n">
-        <v>6731996</v>
+        <v>6732236</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2155,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2137,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spridda över ytan.</t>
+          <t>Spridda över lite större yta.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,45 +2169,59 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130013015</v>
+        <v>130013582</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Österbergs fäbodar, Österbergs fäbodar, Gstr</t>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577777</v>
+        <v>577854</v>
       </c>
       <c r="R15" t="n">
-        <v>6732093</v>
+        <v>6732059</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2267,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2263,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,6 +2287,236 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130013591</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gammelåsstugan, Gammelåsstugan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577858</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6732062</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130033434</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Östbergs Fäbodar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577828</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6732097</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sandviken</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ovansjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52778-2025 artfynd.xlsx
+++ b/artfynd/A 52778-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013237</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013020</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013322</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1224,6 +1249,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013015</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013129</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1443,6 +1478,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013408</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1555,6 +1595,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013075</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1667,6 +1712,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013410</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1793,6 +1843,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130012857</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130012862</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2040,6 +2100,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130012879</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2166,6 +2231,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013164</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2287,6 +2357,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013582</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130013591</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2517,8 +2597,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130033434</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>